--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.5284096631596</v>
+        <v>2.523366570263435</v>
       </c>
       <c r="D2" t="n">
-        <v>4.676418382575396</v>
+        <v>0.7599179871685019</v>
       </c>
       <c r="E2" t="n">
-        <v>17.96297202232417</v>
+        <v>2.918982953627678</v>
       </c>
       <c r="F2" t="n">
-        <v>20.1049989490341</v>
+        <v>3.267062329218042</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.23733363230829</v>
+        <v>9.788566715250097</v>
       </c>
       <c r="D3" t="n">
-        <v>40.0083858731009</v>
+        <v>6.501362704378896</v>
       </c>
       <c r="E3" t="n">
-        <v>17.96297202232417</v>
+        <v>2.918982953627678</v>
       </c>
       <c r="F3" t="n">
-        <v>20.1049989490341</v>
+        <v>3.267062329218042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.66055268798688</v>
+        <v>8.394839811797867</v>
       </c>
       <c r="D4" t="n">
-        <v>46.54218242517168</v>
+        <v>7.563104644090399</v>
       </c>
       <c r="E4" t="n">
-        <v>17.96297202232417</v>
+        <v>2.918982953627678</v>
       </c>
       <c r="F4" t="n">
-        <v>20.1049989490341</v>
+        <v>3.267062329218042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.29343235568294</v>
+        <v>9.310182757798477</v>
       </c>
       <c r="D5" t="n">
-        <v>58.74625936516763</v>
+        <v>9.546267146839741</v>
       </c>
       <c r="E5" t="n">
-        <v>17.96297202232417</v>
+        <v>2.918982953627678</v>
       </c>
       <c r="F5" t="n">
-        <v>20.1049989490341</v>
+        <v>3.267062329218042</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
